--- a/artfynd/A 9838-2023 artfynd.xlsx
+++ b/artfynd/A 9838-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537657</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>5966</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 9838-2023 artfynd.xlsx
+++ b/artfynd/A 9838-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537657</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9838-2023 artfynd.xlsx
+++ b/artfynd/A 9838-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537657</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9838-2023 artfynd.xlsx
+++ b/artfynd/A 9838-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122537657</v>
       </c>
       <c r="B2" t="n">
-        <v>92256</v>
+        <v>92260</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
